--- a/AAII_Financials/Yearly/JEF_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JEF_YR_FIN.xlsx
@@ -2973,10 +2973,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>19804500</v>
+        <v>7647800</v>
       </c>
       <c r="E58" s="3">
-        <v>16559100</v>
+        <v>4221100</v>
       </c>
       <c r="F58" s="3">
         <v>15186200</v>
@@ -3075,10 +3075,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>47557200</v>
+        <v>35400500</v>
       </c>
       <c r="E60" s="3">
-        <v>38124600</v>
+        <v>25786600</v>
       </c>
       <c r="F60" s="3">
         <v>36495000</v>
@@ -3126,10 +3126,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>17720200</v>
+        <v>29877000</v>
       </c>
       <c r="E61" s="3">
-        <v>15931300</v>
+        <v>28269200</v>
       </c>
       <c r="F61" s="3">
         <v>11559300</v>
